--- a/Lab-trails/2026-04-14-density-exp-slurry.xlsx
+++ b/Lab-trails/2026-04-14-density-exp-slurry.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31F5485-2B0B-417B-AE11-6FAFD9727561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8C1D37-3219-4984-AD55-51DD4A7A8733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
-    <sheet name="DM" sheetId="2" r:id="rId2"/>
+    <sheet name="ApplicationRate" sheetId="3" r:id="rId2"/>
+    <sheet name="DM" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -160,6 +161,58 @@
   </si>
   <si>
     <t>NH4-N (diluted) [mg/L]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <t>Cattle slurry untreated</t>
+  </si>
+  <si>
+    <t>Ammonium carbonate std untreated</t>
+  </si>
+  <si>
+    <t>surface area [cm2]</t>
+  </si>
+  <si>
+    <t>surface area [ha]</t>
+  </si>
+  <si>
+    <t>slurry target[g or mL]</t>
+  </si>
+  <si>
+    <t>slurry target [kg or L]</t>
+  </si>
+  <si>
+    <t>Slurry app [L / ha]</t>
+  </si>
+  <si>
+    <t>NH4-N [kg/L]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stdev</t>
+    </r>
+  </si>
+  <si>
+    <t>NH4-N stdev [kg/L]</t>
+  </si>
+  <si>
+    <t>NH4-N app mean [kg/ha]</t>
+  </si>
+  <si>
+    <t>NH4-N app stdev [kg/ha]</t>
   </si>
 </sst>
 </file>
@@ -208,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -217,6 +270,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,6 +796,158 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50306D30-F315-45EA-8286-DA780B683219}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3">
+        <f>TAN!H4</f>
+        <v>2.1795568527859444</v>
+      </c>
+      <c r="C2">
+        <v>0.03</v>
+      </c>
+      <c r="D2" s="1">
+        <f>B2*10^-3</f>
+        <v>2.1795568527859443E-3</v>
+      </c>
+      <c r="E2">
+        <f>C2*10^-3</f>
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <f>F2*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H2">
+        <v>28.27</v>
+      </c>
+      <c r="I2">
+        <f>H2*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J2" s="6">
+        <f>G2/I2</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K2" s="4">
+        <f>D2*J2</f>
+        <v>15.419574480268441</v>
+      </c>
+      <c r="L2" s="4">
+        <f>J2*E2</f>
+        <v>0.21223912274495932</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3">
+        <f>TAN!H7</f>
+        <v>4.2423858670677381</v>
+      </c>
+      <c r="C3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D3" s="1">
+        <f>B3*10^-3</f>
+        <v>4.2423858670677383E-3</v>
+      </c>
+      <c r="E3">
+        <f>C3*10^-3</f>
+        <v>2.8000000000000003E-4</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <f>F3*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H3">
+        <v>28.27</v>
+      </c>
+      <c r="I3">
+        <f>H3*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J3" s="6">
+        <f>G3/I3</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K3" s="4">
+        <f>D3*J3</f>
+        <v>30.013341825735679</v>
+      </c>
+      <c r="L3" s="4">
+        <f>J3*E3</f>
+        <v>1.9808984789529538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A322F488-66DC-4E6C-A2BD-1AE1E849C347}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
